--- a/sample_imports/09_SinhVien_TheoHocKy_Mau.xlsx
+++ b/sample_imports/09_SinhVien_TheoHocKy_Mau.xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="09_SinhVien_TheoHocKy_Mau" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="119">
   <si>
     <t>MSSV</t>
   </si>
@@ -23,31 +23,355 @@
     <t>HoTen</t>
   </si>
   <si>
-    <t>TrangThai</t>
+    <t>MaLop</t>
+  </si>
+  <si>
+    <t>MaHocKy</t>
+  </si>
+  <si>
+    <t>SoTinChiTichLuy</t>
+  </si>
+  <si>
+    <t>DiemTichLuy</t>
   </si>
   <si>
     <t>GhiChu</t>
   </si>
   <si>
+    <t>2001210001</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoàng Long</t>
+  </si>
+  <si>
+    <t>12DHCNTT01</t>
+  </si>
+  <si>
+    <t>HK2627_1</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>3.45</t>
+  </si>
+  <si>
+    <t>Đủ điều kiện làm khóa luận tốt nghiệp - Đã công bố</t>
+  </si>
+  <si>
+    <t>2001210002</t>
+  </si>
+  <si>
+    <t>Trần Minh Quân</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>3.20</t>
+  </si>
+  <si>
+    <t>2001210003</t>
+  </si>
+  <si>
+    <t>Lê Phương Anh</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>3.65</t>
+  </si>
+  <si>
+    <t>2001210004</t>
+  </si>
+  <si>
+    <t>Phạm Đức Duy</t>
+  </si>
+  <si>
+    <t>12DHCNTT02</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>3.10</t>
+  </si>
+  <si>
+    <t>2001210005</t>
+  </si>
+  <si>
+    <t>Hoàng Thùy Linh</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>3.52</t>
+  </si>
+  <si>
+    <t>2001210006</t>
+  </si>
+  <si>
+    <t>Huỳnh Quốc Huy</t>
+  </si>
+  <si>
+    <t>12DHKPM01</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>3.70</t>
+  </si>
+  <si>
+    <t>2001210007</t>
+  </si>
+  <si>
+    <t>Võ Thị Kim Ngân</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>3.15</t>
+  </si>
+  <si>
+    <t>2001210008</t>
+  </si>
+  <si>
+    <t>Đặng Thành Nam</t>
+  </si>
+  <si>
+    <t>12DHHTTT01</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>3.28</t>
+  </si>
+  <si>
+    <t>2001210009</t>
+  </si>
+  <si>
+    <t>Bùi Thị Thanh Hằng</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>3.60</t>
+  </si>
+  <si>
+    <t>2001210010</t>
+  </si>
+  <si>
+    <t>Đỗ Trọng Hiếu</t>
+  </si>
+  <si>
+    <t>12DHATTT01</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>3.35</t>
+  </si>
+  <si>
+    <t>2001210011</t>
+  </si>
+  <si>
+    <t>Hồ Diệu Linh</t>
+  </si>
+  <si>
+    <t>3.22</t>
+  </si>
+  <si>
+    <t>2001210012</t>
+  </si>
+  <si>
+    <t>Ngô Văn Tuấn</t>
+  </si>
+  <si>
+    <t>12DHKHMT01</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>3.85</t>
+  </si>
+  <si>
+    <t>2001210013</t>
+  </si>
+  <si>
+    <t>Dương Bảo Ngọc</t>
+  </si>
+  <si>
+    <t>3.58</t>
+  </si>
+  <si>
+    <t>2001210042</t>
+  </si>
+  <si>
+    <t>Nông Đức Mạnh</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>3.05</t>
+  </si>
+  <si>
+    <t>2001210043</t>
+  </si>
+  <si>
+    <t>Lục Hải Yến</t>
+  </si>
+  <si>
+    <t>134</t>
+  </si>
+  <si>
+    <t>3.75</t>
+  </si>
+  <si>
+    <t>2001210044</t>
+  </si>
+  <si>
     <t>Châu Gia Hưng</t>
   </si>
   <si>
-    <t>Đủ điều kiện</t>
-  </si>
-  <si>
-    <t>Đủ điều kiện làm khóa luận tốt nghiệp</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Hoa</t>
-  </si>
-  <si>
-    <t>Chưa đủ điều kiện</t>
-  </si>
-  <si>
-    <t>Thiếu tín chỉ tích lũy (105/115)</t>
-  </si>
-  <si>
-    <t>Trần Văn Nam</t>
+    <t>3.32</t>
+  </si>
+  <si>
+    <t>2001210045</t>
+  </si>
+  <si>
+    <t>Mạc Quỳnh Giao</t>
+  </si>
+  <si>
+    <t>2001210046</t>
+  </si>
+  <si>
+    <t>Phí Trọng Nhân</t>
+  </si>
+  <si>
+    <t>133</t>
+  </si>
+  <si>
+    <t>3.68</t>
+  </si>
+  <si>
+    <t>2001210060</t>
+  </si>
+  <si>
+    <t>Bùi Gia Bảo</t>
+  </si>
+  <si>
+    <t>3.25</t>
+  </si>
+  <si>
+    <t>2001210061</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Châu</t>
+  </si>
+  <si>
+    <t>2001210062</t>
+  </si>
+  <si>
+    <t>Đặng Quốc Dũng</t>
+  </si>
+  <si>
+    <t>2001210063</t>
+  </si>
+  <si>
+    <t>Lê Hoàng Giang</t>
+  </si>
+  <si>
+    <t>2001210064</t>
+  </si>
+  <si>
+    <t>Vũ Thúy Hạnh</t>
+  </si>
+  <si>
+    <t>2001210065</t>
+  </si>
+  <si>
+    <t>Phạm Quang Huy</t>
+  </si>
+  <si>
+    <t>2001210066</t>
+  </si>
+  <si>
+    <t>Đỗ Tuấn Kiệt</t>
+  </si>
+  <si>
+    <t>2001210067</t>
+  </si>
+  <si>
+    <t>Trịnh Mai Linh</t>
+  </si>
+  <si>
+    <t>2001210068</t>
+  </si>
+  <si>
+    <t>Ngô Minh Nhật</t>
+  </si>
+  <si>
+    <t>2001210069</t>
+  </si>
+  <si>
+    <t>Hoàng Yến Nhi</t>
+  </si>
+  <si>
+    <t>2001210070</t>
+  </si>
+  <si>
+    <t>Phan Thanh Phong</t>
+  </si>
+  <si>
+    <t>2001210071</t>
+  </si>
+  <si>
+    <t>Lương Hồng Phúc</t>
+  </si>
+  <si>
+    <t>2001210072</t>
+  </si>
+  <si>
+    <t>Võ Hữu Quân</t>
+  </si>
+  <si>
+    <t>2001210073</t>
+  </si>
+  <si>
+    <t>Mai Ngọc Sơn</t>
+  </si>
+  <si>
+    <t>2001210074</t>
+  </si>
+  <si>
+    <t>Đinh Phương Thảo</t>
+  </si>
+  <si>
+    <t>2001210075</t>
+  </si>
+  <si>
+    <t>Hà Đức Trọng</t>
+  </si>
+  <si>
+    <t>2001230136</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Thùy Dương</t>
+  </si>
+  <si>
+    <t>3.50</t>
+  </si>
+  <si>
+    <t>Tạo mới hồ sơ &amp; cấp tài khoản vào học kỳ</t>
   </si>
 </sst>
 </file>
@@ -55,7 +379,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -65,16 +389,31 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00529B"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -82,12 +421,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="2" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -387,60 +762,845 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="25.851" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="20.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="16.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="60.128" bestFit="true" customWidth="true" style="0"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" customHeight="1" ht="28">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
-        <v>2001210041</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3">
-        <v>2001210042</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4">
-        <v>2001210043</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4"/>
-      <c r="D4"/>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
